--- a/output_data/charts/crashSeverityByType-Franklin.xlsx
+++ b/output_data/charts/crashSeverityByType-Franklin.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Share of fatal crashes</t>
   </si>
@@ -34,12 +34,12 @@
     <t>Fixed Object</t>
   </si>
   <si>
+    <t>Angle</t>
+  </si>
+  <si>
     <t>Head On</t>
   </si>
   <si>
-    <t>Angle</t>
-  </si>
-  <si>
     <t>Left Turn</t>
   </si>
   <si>
@@ -61,25 +61,22 @@
     <t>Other Non-Collision</t>
   </si>
   <si>
+    <t>Animal</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
     <t>Right Turn</t>
   </si>
   <si>
-    <t>Animal</t>
-  </si>
-  <si>
-    <t>Unknown</t>
-  </si>
-  <si>
     <t>Other Object</t>
   </si>
   <si>
+    <t>Sideswipe - Meeting</t>
+  </si>
+  <si>
     <t>Backing</t>
-  </si>
-  <si>
-    <t>Falling From Or In Vehicle</t>
-  </si>
-  <si>
-    <t>Sideswipe - Meeting</t>
   </si>
   <si>
     <t>Train</t>
@@ -215,9 +212,9 @@
           </c:spPr>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$2:$A$20</c:f>
+              <c:f>Sheet1!$A$2:$A$19</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>Pedestrian</c:v>
                 </c:pt>
@@ -225,10 +222,10 @@
                   <c:v>Fixed Object</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Angle</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Head On</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Angle</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Left Turn</c:v>
@@ -252,27 +249,24 @@
                   <c:v>Other Non-Collision</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>Animal</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Unknown</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>Right Turn</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Animal</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Unknown</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>Other Object</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>Sideswipe - Meeting</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>Backing</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>Falling From Or In Vehicle</c:v>
-                </c:pt>
                 <c:pt idx="17">
-                  <c:v>Sideswipe - Meeting</c:v>
-                </c:pt>
-                <c:pt idx="18">
                   <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
@@ -280,54 +274,54 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$20</c:f>
+              <c:f>Sheet1!$B$2:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>26.3986013986014</c:v>
+                  <c:v>26.53429602888087</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24.65034965034965</c:v>
+                  <c:v>23.46570397111913</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.48951048951049</c:v>
+                  <c:v>12.09386281588448</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.965034965034965</c:v>
+                  <c:v>10.10830324909747</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.342657342657342</c:v>
+                  <c:v>7.039711191335741</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.643356643356643</c:v>
+                  <c:v>7.039711191335741</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.769230769230769</c:v>
+                  <c:v>6.137184115523466</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.447552447552447</c:v>
+                  <c:v>2.166064981949458</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.748251748251748</c:v>
+                  <c:v>1.624548736462094</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.573426573426574</c:v>
+                  <c:v>1.263537906137184</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.223776223776224</c:v>
+                  <c:v>0.9025270758122743</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.6993006993006993</c:v>
+                  <c:v>0.5415162454873645</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.5244755244755245</c:v>
+                  <c:v>0.5415162454873645</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.3496503496503496</c:v>
+                  <c:v>0.3610108303249098</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.1748251748251748</c:v>
+                  <c:v>0.1805054151624549</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
@@ -336,9 +330,6 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -369,9 +360,9 @@
           </c:spPr>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$2:$A$20</c:f>
+              <c:f>Sheet1!$A$2:$A$19</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>Pedestrian</c:v>
                 </c:pt>
@@ -379,10 +370,10 @@
                   <c:v>Fixed Object</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Angle</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Head On</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Angle</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Left Turn</c:v>
@@ -406,27 +397,24 @@
                   <c:v>Other Non-Collision</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>Animal</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Unknown</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>Right Turn</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Animal</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Unknown</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>Other Object</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>Sideswipe - Meeting</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>Backing</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>Falling From Or In Vehicle</c:v>
-                </c:pt>
                 <c:pt idx="17">
-                  <c:v>Sideswipe - Meeting</c:v>
-                </c:pt>
-                <c:pt idx="18">
                   <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
@@ -434,66 +422,63 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$20</c:f>
+              <c:f>Sheet1!$C$2:$C$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>15.46212647671994</c:v>
+                  <c:v>16.80401289860265</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>19.35371785962474</c:v>
+                  <c:v>19.24041562164099</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.443363446838081</c:v>
+                  <c:v>16.80401289860265</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>17.02571230020848</c:v>
+                  <c:v>8.599068434252956</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.887421820708826</c:v>
+                  <c:v>7.560014331780724</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.29256428075052</c:v>
+                  <c:v>10.49802938015048</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.78318276580959</c:v>
+                  <c:v>7.165890361877464</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.509381514940931</c:v>
+                  <c:v>3.86958079541383</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.772063933287005</c:v>
+                  <c:v>1.791472590469366</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.744961779013204</c:v>
+                  <c:v>2.973844500179147</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.980542043085476</c:v>
+                  <c:v>1.934790397706915</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.42460041695622</c:v>
+                  <c:v>0.107488355428162</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.1042390548992356</c:v>
+                  <c:v>0.6449301325689717</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.5559416261292565</c:v>
+                  <c:v>1.289860265137943</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.2432244614315497</c:v>
+                  <c:v>0.2149767108563239</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.3822098679638638</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>0.4657828735220351</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.03474635163307853</c:v>
+                  <c:v>0.03582945180938731</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -523,9 +508,9 @@
           </c:spPr>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$A$2:$A$20</c:f>
+              <c:f>Sheet1!$A$2:$A$19</c:f>
               <c:strCache>
-                <c:ptCount val="19"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>Pedestrian</c:v>
                 </c:pt>
@@ -533,10 +518,10 @@
                   <c:v>Fixed Object</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Angle</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Head On</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Angle</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Left Turn</c:v>
@@ -560,27 +545,24 @@
                   <c:v>Other Non-Collision</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>Animal</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Unknown</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>Right Turn</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Animal</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Unknown</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>Other Object</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>Sideswipe - Meeting</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>Backing</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>Falling From Or In Vehicle</c:v>
-                </c:pt>
                 <c:pt idx="17">
-                  <c:v>Sideswipe - Meeting</c:v>
-                </c:pt>
-                <c:pt idx="18">
                   <c:v>Train</c:v>
                 </c:pt>
               </c:strCache>
@@ -588,66 +570,63 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$20</c:f>
+              <c:f>Sheet1!$D$2:$D$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="19"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>1.922231195477479</c:v>
+                  <c:v>2.140091394286113</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>11.85162678010283</c:v>
+                  <c:v>12.53008685945512</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.114134476223983</c:v>
+                  <c:v>16.65329472913106</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16.01752716630818</c:v>
+                  <c:v>2.305787142009976</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.10202058162686</c:v>
+                  <c:v>7.2417762584156</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>25.10254831564891</c:v>
+                  <c:v>23.05002267415495</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>17.40722675771411</c:v>
+                  <c:v>17.14689364077162</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.73962722787715</c:v>
+                  <c:v>0.7831304287159452</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.3566202633872528</c:v>
+                  <c:v>0.3906931314752154</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.978378897035894</c:v>
+                  <c:v>8.116475389821048</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.021884969975132</c:v>
+                  <c:v>1.103184846687829</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.267952951712337</c:v>
+                  <c:v>0.7316775386332717</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.7340300488553769</c:v>
+                  <c:v>0.565981790909408</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.4821569928755907</c:v>
+                  <c:v>3.270310810339415</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.3326323532939399</c:v>
+                  <c:v>0.3610423134614714</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.524623589710786</c:v>
+                  <c:v>0.04098789548958733</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.0007995970031104322</c:v>
+                  <c:v>3.559842327414797</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.03838065614930075</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.005597179021773027</c:v>
+                  <c:v>0.008720828827571771</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1075,7 +1054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" style="1" customWidth="1"/>
@@ -1103,13 +1082,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>26.3986013986014</v>
+        <v>26.53429602888087</v>
       </c>
       <c r="C2" s="2">
-        <v>15.46212647671994</v>
+        <v>16.80401289860265</v>
       </c>
       <c r="D2" s="2">
-        <v>1.922231195477479</v>
+        <v>2.140091394286113</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1117,13 +1096,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>24.65034965034965</v>
+        <v>23.46570397111913</v>
       </c>
       <c r="C3" s="2">
-        <v>19.35371785962474</v>
+        <v>19.24041562164099</v>
       </c>
       <c r="D3" s="2">
-        <v>11.85162678010283</v>
+        <v>12.53008685945512</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1131,13 +1110,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>10.48951048951049</v>
+        <v>12.09386281588448</v>
       </c>
       <c r="C4" s="2">
-        <v>8.443363446838081</v>
+        <v>16.80401289860265</v>
       </c>
       <c r="D4" s="2">
-        <v>2.114134476223983</v>
+        <v>16.65329472913106</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1145,13 +1124,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2">
-        <v>9.965034965034965</v>
+        <v>10.10830324909747</v>
       </c>
       <c r="C5" s="2">
-        <v>17.02571230020848</v>
+        <v>8.599068434252956</v>
       </c>
       <c r="D5" s="2">
-        <v>16.01752716630818</v>
+        <v>2.305787142009976</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1159,13 +1138,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>7.342657342657342</v>
+        <v>7.039711191335741</v>
       </c>
       <c r="C6" s="2">
-        <v>7.887421820708826</v>
+        <v>7.560014331780724</v>
       </c>
       <c r="D6" s="2">
-        <v>7.10202058162686</v>
+        <v>7.2417762584156</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1173,13 +1152,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2">
-        <v>6.643356643356643</v>
+        <v>7.039711191335741</v>
       </c>
       <c r="C7" s="2">
-        <v>11.29256428075052</v>
+        <v>10.49802938015048</v>
       </c>
       <c r="D7" s="2">
-        <v>25.10254831564891</v>
+        <v>23.05002267415495</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1187,13 +1166,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2">
-        <v>5.769230769230769</v>
+        <v>6.137184115523466</v>
       </c>
       <c r="C8" s="2">
-        <v>7.78318276580959</v>
+        <v>7.165890361877464</v>
       </c>
       <c r="D8" s="2">
-        <v>17.40722675771411</v>
+        <v>17.14689364077162</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1201,13 +1180,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2">
-        <v>2.447552447552447</v>
+        <v>2.166064981949458</v>
       </c>
       <c r="C9" s="2">
-        <v>3.509381514940931</v>
+        <v>3.86958079541383</v>
       </c>
       <c r="D9" s="2">
-        <v>0.73962722787715</v>
+        <v>0.7831304287159452</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1215,13 +1194,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2">
-        <v>1.748251748251748</v>
+        <v>1.624548736462094</v>
       </c>
       <c r="C10" s="2">
-        <v>1.772063933287005</v>
+        <v>1.791472590469366</v>
       </c>
       <c r="D10" s="2">
-        <v>0.3566202633872528</v>
+        <v>0.3906931314752154</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1229,13 +1208,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2">
-        <v>1.573426573426574</v>
+        <v>1.263537906137184</v>
       </c>
       <c r="C11" s="2">
-        <v>2.744961779013204</v>
+        <v>2.973844500179147</v>
       </c>
       <c r="D11" s="2">
-        <v>7.978378897035894</v>
+        <v>8.116475389821048</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1243,13 +1222,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2">
-        <v>1.223776223776224</v>
+        <v>0.9025270758122743</v>
       </c>
       <c r="C12" s="2">
-        <v>1.980542043085476</v>
+        <v>1.934790397706915</v>
       </c>
       <c r="D12" s="2">
-        <v>1.021884969975132</v>
+        <v>1.103184846687829</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1257,13 +1236,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2">
-        <v>0.6993006993006993</v>
+        <v>0.5415162454873645</v>
       </c>
       <c r="C13" s="2">
-        <v>1.42460041695622</v>
+        <v>0.107488355428162</v>
       </c>
       <c r="D13" s="2">
-        <v>3.267952951712337</v>
+        <v>0.7316775386332717</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1271,13 +1250,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="2">
-        <v>0.5244755244755245</v>
+        <v>0.5415162454873645</v>
       </c>
       <c r="C14" s="2">
-        <v>0.1042390548992356</v>
+        <v>0.6449301325689717</v>
       </c>
       <c r="D14" s="2">
-        <v>0.7340300488553769</v>
+        <v>0.565981790909408</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1285,13 +1264,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="2">
-        <v>0.3496503496503496</v>
+        <v>0.3610108303249098</v>
       </c>
       <c r="C15" s="2">
-        <v>0.5559416261292565</v>
+        <v>1.289860265137943</v>
       </c>
       <c r="D15" s="2">
-        <v>0.4821569928755907</v>
+        <v>3.270310810339415</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1299,13 +1278,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="2">
-        <v>0.1748251748251748</v>
+        <v>0.1805054151624549</v>
       </c>
       <c r="C16" s="2">
-        <v>0.2432244614315497</v>
+        <v>0.2149767108563239</v>
       </c>
       <c r="D16" s="2">
-        <v>0.3326323532939399</v>
+        <v>0.3610423134614714</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1316,10 +1295,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="2">
-        <v>0.3822098679638638</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>3.524623589710786</v>
+        <v>0.04098789548958733</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1330,10 +1309,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="2">
-        <v>0</v>
+        <v>0.4657828735220351</v>
       </c>
       <c r="D18" s="2">
-        <v>0.0007995970031104322</v>
+        <v>3.559842327414797</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1344,24 +1323,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="2">
-        <v>0</v>
+        <v>0.03582945180938731</v>
       </c>
       <c r="D19" s="2">
-        <v>0.03838065614930075</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="2">
-        <v>0</v>
-      </c>
-      <c r="C20" s="2">
-        <v>0.03474635163307853</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0.005597179021773027</v>
+        <v>0.008720828827571771</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/crashSeverityByType-Franklin.xlsx
+++ b/output_data/charts/crashSeverityByType-Franklin.xlsx
@@ -86,8 +86,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode=""/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -144,7 +145,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -176,7 +177,7 @@
               <a:rPr lang="en-US" sz="1400" baseline="0">
                 <a:latin typeface="Arial"/>
               </a:rPr>
-              <a:t>Crash Severity by Type of Crash - Franklin County</a:t>
+              <a:t>Crash Severity by Type of Crash, Franklin County, 2020-2024</a:t>
             </a:r>
           </a:p>
         </c:rich>
